--- a/reports/2026-09_月次実績報告/excel/第51期下期石見営業所担当者別実績.xlsx
+++ b/reports/2026-09_月次実績報告/excel/第51期下期石見営業所担当者別実績.xlsx
@@ -22704,10 +22704,10 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>20822</v>
+        <v>20822.257</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>16655</v>
+        <v>16655.218</v>
       </c>
       <c r="G77" s="115" t="n">
         <v>17972.437</v>
@@ -22726,10 +22726,10 @@
         <v/>
       </c>
       <c r="L77" s="3" t="n">
-        <v>5383</v>
+        <v>5382.5816</v>
       </c>
       <c r="M77" s="4" t="n">
-        <v>4616</v>
+        <v>4615.536</v>
       </c>
       <c r="N77" s="115" t="n">
         <v>4733.414</v>
@@ -22788,10 +22788,10 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>12178</v>
+        <v>12178.374</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>8823</v>
+        <v>8822.834999999999</v>
       </c>
       <c r="G78" s="115" t="n">
         <v>13608.228</v>
@@ -22810,10 +22810,10 @@
         <v/>
       </c>
       <c r="L78" s="3" t="n">
-        <v>3649</v>
+        <v>3649.391</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>2821</v>
+        <v>2821.493</v>
       </c>
       <c r="N78" s="115" t="n">
         <v>3615.586</v>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>31842</v>
+        <v>31841.832</v>
       </c>
       <c r="F80" s="4" t="n">
         <v>20938.857</v>
@@ -22978,7 +22978,7 @@
         <v/>
       </c>
       <c r="L80" s="3" t="n">
-        <v>8288</v>
+        <v>8287.544400000001</v>
       </c>
       <c r="M80" s="4" t="n">
         <v>5685.361</v>
